--- a/artfynd/A 28141-2026 artfynd.xlsx
+++ b/artfynd/A 28141-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135041204</v>
+        <v>135160025</v>
       </c>
       <c r="B9" t="n">
-        <v>8460</v>
+        <v>57972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,37 +1365,45 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stora Bogölen, Stora Bogölen, Ög</t>
+          <t>Stora Bogölen, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>567923</v>
+        <v>567893</v>
       </c>
       <c r="R9" t="n">
-        <v>6509408</v>
+        <v>6509429</v>
       </c>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1425,6 +1433,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>I död liggande asp</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1439,15 +1452,662 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135160364</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stora Bogölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>567761</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6509360</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Både färska och äldre födosöksspår i tallraka</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135160742</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stora Bogölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>567756</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6509401</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Fyra döda liggande granar, med färska födosökspår</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135160755</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Stora Bogölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>567754</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6509418</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska födosökspår i liggande död björk</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135041204</v>
+      </c>
+      <c r="B13" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Stora Bogölen, Stora Bogölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>567923</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6509408</v>
+      </c>
+      <c r="S13" t="n">
+        <v>13</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
           <t>Eva Siljeholm</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AX13" t="inlineStr">
         <is>
           <t>Eva Siljeholm</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135160100</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Stora Bogölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>567767</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6509480</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135159606</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stora Bogölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>567904</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6509341</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anette Källman, Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28141-2026 artfynd.xlsx
+++ b/artfynd/A 28141-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135046154</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135040549</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135040572</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135041044</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135040605</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135039197</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135039853</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1461,6 +1501,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135160025</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1571,6 +1616,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135160364</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1681,6 +1731,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135160742</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1791,6 +1846,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135160755</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1888,6 +1948,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135041204</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1998,6 +2063,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135160100</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2108,8 +2178,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135159606</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 28141-2026 artfynd.xlsx
+++ b/artfynd/A 28141-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135046154</v>
       </c>
       <c r="B2" t="n">
-        <v>92647</v>
+        <v>92689</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135040549</v>
       </c>
       <c r="B3" t="n">
-        <v>96512</v>
+        <v>96556</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135040572</v>
       </c>
       <c r="B4" t="n">
-        <v>96501</v>
+        <v>96545</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135041044</v>
       </c>
       <c r="B5" t="n">
-        <v>96501</v>
+        <v>96545</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135040605</v>
       </c>
       <c r="B6" t="n">
-        <v>96306</v>
+        <v>96350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135039197</v>
       </c>
       <c r="B7" t="n">
-        <v>92385</v>
+        <v>92427</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135039853</v>
       </c>
       <c r="B8" t="n">
-        <v>91995</v>
+        <v>92037</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135160025</v>
       </c>
       <c r="B9" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>135160364</v>
       </c>
       <c r="B10" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>135160742</v>
       </c>
       <c r="B11" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>135160755</v>
       </c>
       <c r="B12" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>135041204</v>
       </c>
       <c r="B13" t="n">
-        <v>8460</v>
+        <v>8461</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>135160100</v>
       </c>
       <c r="B14" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>135159606</v>
       </c>
       <c r="B15" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 28141-2026 artfynd.xlsx
+++ b/artfynd/A 28141-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135046154</v>
       </c>
       <c r="B2" t="n">
-        <v>92689</v>
+        <v>92716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135040549</v>
       </c>
       <c r="B3" t="n">
-        <v>96556</v>
+        <v>96583</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135040572</v>
       </c>
       <c r="B4" t="n">
-        <v>96545</v>
+        <v>96572</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135041044</v>
       </c>
       <c r="B5" t="n">
-        <v>96545</v>
+        <v>96572</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135040605</v>
       </c>
       <c r="B6" t="n">
-        <v>96350</v>
+        <v>96377</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135039197</v>
       </c>
       <c r="B7" t="n">
-        <v>92427</v>
+        <v>92454</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135039853</v>
       </c>
       <c r="B8" t="n">
-        <v>92037</v>
+        <v>92064</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>135160100</v>
       </c>
       <c r="B14" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>135159606</v>
       </c>
       <c r="B15" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
